--- a/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
+++ b/sources/metaPee/combined/subexposure_views/no/Plot/exposures_meta_analysis_renal_cell_carcinoma_combined.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Analysis mode" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K39"/>
+  <dimension ref="A1:K44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,34 +831,34 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0.8</v>
+        <v>0.79</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.49</v>
+        <v>0.53</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.04</v>
+        <v>0.97</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>54.1</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.0063872031972724</v>
+        <v>0.002721921548332925</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>2782705</v>
+        <v>3783725</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>21572</v>
+        <v>24558</v>
       </c>
     </row>
     <row r="13">
@@ -1239,34 +1239,34 @@
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C24" s="3" t="n">
         <v>0.82</v>
       </c>
       <c r="D24" s="3" t="n">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="E24" s="3" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>1.52</v>
+        <v>1.46</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>65.8</v>
+        <v>61.3</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>0.9611183115273437</v>
+        <v>0.8716110510016006</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>152396</v>
+        <v>153812</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>2605</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="25">
@@ -1476,181 +1476,181 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>processed_meat_intake</t>
+          <t>animal_protein_intake</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>1.13</v>
+        <v>1.05</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="F31" s="3" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="G31" s="3" t="n">
-        <v>2.32</v>
-      </c>
+        <v>1.28</v>
+      </c>
+      <c r="F31" s="3" t="inlineStr"/>
+      <c r="G31" s="3" t="inlineStr"/>
       <c r="H31" s="4" t="n">
-        <v>75.59999999999999</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>0.02775832913849235</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="2" t="n">
-        <v>991708</v>
+        <v>774952</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3734</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>vitamin_a</t>
+          <t>monounsaturated_fat_mufa</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C32" s="3" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="D32" s="3" t="n">
-        <v>0.53</v>
+        <v>0.92</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>2.8</v>
+        <v>1.32</v>
       </c>
       <c r="F32" s="3" t="inlineStr"/>
       <c r="G32" s="3" t="inlineStr"/>
       <c r="H32" s="4" t="n">
-        <v>92.7</v>
+        <v>0</v>
       </c>
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="2" t="n">
-        <v>4597</v>
+        <v>774952</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>1909</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>dietary_protein_intake</t>
+          <t>polyunsaturated_fat_pufa</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C33" s="3" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="D33" s="3" t="n">
-        <v>0.76</v>
+        <v>0.93</v>
       </c>
       <c r="E33" s="3" t="n">
-        <v>2.22</v>
+        <v>1.31</v>
       </c>
       <c r="F33" s="3" t="inlineStr"/>
       <c r="G33" s="3" t="inlineStr"/>
       <c r="H33" s="4" t="n">
-        <v>66.7</v>
+        <v>0</v>
       </c>
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="2" t="n">
-        <v>776349</v>
+        <v>774952</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2168</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>yogurt</t>
+          <t>processed_meat_intake</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>1.3</v>
+        <v>1.15</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>1.03</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="F34" s="3" t="inlineStr"/>
-      <c r="G34" s="3" t="inlineStr"/>
+        <v>1.41</v>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>2.09</v>
+      </c>
       <c r="H34" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="5" t="inlineStr"/>
+        <v>77.09999999999999</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>0.009042172378070409</v>
+      </c>
       <c r="J34" s="2" t="n">
-        <v>1812</v>
+        <v>1766660</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>777</v>
+        <v>5212</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>docosahexaenoic_acid</t>
+          <t>vitamin_a</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C35" s="3" t="n">
-        <v>1.55</v>
+        <v>1.22</v>
       </c>
       <c r="D35" s="3" t="n">
-        <v>1.07</v>
+        <v>0.53</v>
       </c>
       <c r="E35" s="3" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="F35" s="3" t="inlineStr"/>
       <c r="G35" s="3" t="inlineStr"/>
       <c r="H35" s="4" t="n">
-        <v>0</v>
+        <v>92.7</v>
       </c>
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="2" t="n">
-        <v>84063</v>
+        <v>4597</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>262</v>
+        <v>1909</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>omega_3_fatty_acids</t>
+          <t>potassium</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>1.55</v>
+        <v>1.28</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.07</v>
+        <v>0.87</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>2.26</v>
+        <v>1.89</v>
       </c>
       <c r="F36" s="3" t="inlineStr"/>
       <c r="G36" s="3" t="inlineStr"/>
@@ -1659,66 +1659,60 @@
       </c>
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="2" t="n">
-        <v>84063</v>
+        <v>120852</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>262</v>
+        <v>485</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>red_meat</t>
+          <t>dietary_protein_intake</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C37" s="3" t="n">
-        <v>1.76</v>
+        <v>1.3</v>
       </c>
       <c r="D37" s="3" t="n">
-        <v>1.22</v>
+        <v>0.76</v>
       </c>
       <c r="E37" s="3" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>8.18</v>
-      </c>
+        <v>2.22</v>
+      </c>
+      <c r="F37" s="3" t="inlineStr"/>
+      <c r="G37" s="3" t="inlineStr"/>
       <c r="H37" s="4" t="n">
-        <v>83</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>0.02775124316058075</v>
-      </c>
+        <v>66.7</v>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="2" t="n">
-        <v>986845</v>
+        <v>776349</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3043</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>oleic_acid</t>
+          <t>yogurt</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
         <v>1</v>
       </c>
       <c r="C38" s="3" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="D38" s="3" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
       <c r="E38" s="3" t="n">
-        <v>2.81</v>
+        <v>1.65</v>
       </c>
       <c r="F38" s="3" t="inlineStr"/>
       <c r="G38" s="3" t="inlineStr"/>
@@ -1727,51 +1721,212 @@
       </c>
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="2" t="n">
-        <v>2143</v>
+        <v>1812</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>323</v>
+        <v>777</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>red_meat</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>0.01699728030121729</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1768446</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>5800</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>docosahexaenoic_acid</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr"/>
+      <c r="G40" s="3" t="inlineStr"/>
+      <c r="H40" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="2" t="n">
+        <v>84063</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>omega_3_fatty_acids</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="F41" s="3" t="inlineStr"/>
+      <c r="G41" s="3" t="inlineStr"/>
+      <c r="H41" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="2" t="n">
+        <v>84063</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>oleic_acid</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="2" t="n">
+        <v>2143</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>carnitine</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="F43" s="3" t="inlineStr"/>
+      <c r="G43" s="3" t="inlineStr"/>
+      <c r="H43" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="2" t="n">
+        <v>534</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>dairy</t>
         </is>
       </c>
-      <c r="B39" s="2" t="n">
+      <c r="B44" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="C44" s="3" t="n">
         <v>2.79</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>1.24</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>6.32</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="3" t="n">
+      <c r="F44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G44" s="3" t="n">
         <v>38266.15</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H44" s="4" t="n">
         <v>78.5</v>
       </c>
-      <c r="I39" s="5" t="n">
+      <c r="I44" s="5" t="n">
         <v>0.1478178443329679</v>
       </c>
-      <c r="J39" s="2" t="n">
+      <c r="J44" s="2" t="n">
         <v>3506</v>
       </c>
-      <c r="K39" s="2" t="n">
+      <c r="K44" s="2" t="n">
         <v>1009</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K44"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
